--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_46.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_14_46.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5461667.49949504</v>
+        <v>5421641.40674164</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645786</v>
+        <v>6767152.318645784</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645786</v>
+        <v>6767152.318645784</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517472</v>
+        <v>2916902.906517485</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517472</v>
+        <v>2916902.906517485</v>
       </c>
     </row>
     <row r="11">
@@ -663,7 +663,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
@@ -675,13 +675,13 @@
         <v>408.0096587035274</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
-        <v>418.7382696589336</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>97.12488247690067</v>
+        <v>97.12488247690055</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -690,22 +690,22 @@
         <v>297.9910820919849</v>
       </c>
       <c r="N2" t="n">
-        <v>410.61515471427</v>
+        <v>814</v>
       </c>
       <c r="O2" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>814</v>
+        <v>418.7212354311146</v>
       </c>
       <c r="Q2" t="n">
-        <v>370.9706110579117</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>337.5389603594425</v>
+        <v>438.3363995050528</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -714,7 +714,7 @@
         <v>249.2212965486107</v>
       </c>
       <c r="V2" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
         <v>238.3734759809475</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>314.8597026170468</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S3" t="n">
-        <v>466.5639999646113</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
         <v>5.357765217513816</v>
@@ -793,7 +793,7 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
-        <v>72.23629157494248</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>114.9691617060979</v>
+        <v>114.9691617061055</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -909,7 +909,7 @@
         <v>403.7573722870162</v>
       </c>
       <c r="H5" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
@@ -921,31 +921,31 @@
         <v>97.12488247690067</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M5" t="n">
+        <v>297.9910820919849</v>
+      </c>
+      <c r="N5" t="n">
+        <v>410.6151547142691</v>
+      </c>
+      <c r="O5" t="n">
         <v>814</v>
       </c>
-      <c r="N5" t="n">
-        <v>814</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
-        <v>281.775447864166</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>797.8013999999999</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
-        <v>279.2852146029995</v>
+        <v>530.163813431294</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -960,7 +960,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -982,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1027,16 +1027,16 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2103597601867477</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X6" t="n">
-        <v>212.2125856159061</v>
+        <v>77.58836382881032</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>297.3920501269237</v>
+        <v>297.3920501269269</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>351.4978904062565</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -1155,46 +1155,46 @@
         <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>97.12488247690067</v>
+        <v>313.1545016101229</v>
       </c>
       <c r="L8" t="n">
-        <v>410.6151547142739</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>297.9910820919849</v>
       </c>
       <c r="N8" t="n">
-        <v>814</v>
+        <v>194.5855355810472</v>
       </c>
       <c r="O8" t="n">
         <v>814</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q8" t="n">
         <v>370.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
-        <v>229.8510241668239</v>
+        <v>322.4606570412591</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>192.2818334606677</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y8" t="n">
         <v>111.3174326828064</v>
@@ -1213,16 +1213,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>189.3139912864827</v>
+        <v>175.4172848236332</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>120.6316114025499</v>
+        <v>114.969161706095</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>297.3920501269246</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1368,16 +1368,16 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>163.185320105538</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>169.1611862385191</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1565,13 +1565,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>153.8896287080119</v>
+        <v>67.57968198731129</v>
       </c>
       <c r="G14" t="n">
-        <v>152.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>8.427217891264409</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T14" t="n">
         <v>335.6755817285639</v>
@@ -1799,16 +1799,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>92.1326498274306</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.97841917455702</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1851,10 +1851,10 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>125.8896287080119</v>
+        <v>125.4590200934258</v>
       </c>
       <c r="G17" t="n">
-        <v>124.3267636724302</v>
+        <v>124.7573722870162</v>
       </c>
       <c r="H17" t="n">
         <v>129.0096587035274</v>
@@ -2088,7 +2088,7 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>125.4590200934258</v>
+        <v>125.8896287080119</v>
       </c>
       <c r="G20" t="n">
         <v>124.7573722870162</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T20" t="n">
         <v>307.6755817285639</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>225.1315699588404</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2276,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>215.4175591878056</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T23" t="n">
         <v>307.6755817285639</v>
@@ -2510,16 +2510,16 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>16.3474343746833</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>185.3391557398498</v>
@@ -2598,19 +2598,19 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>4.467888059376327</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
         <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>413.3734759809475</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>31.61120487365793</v>
       </c>
     </row>
     <row r="27">
@@ -2744,13 +2744,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2802,10 +2802,10 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>178.7573722870162</v>
+        <v>114.414487898597</v>
       </c>
       <c r="H29" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2841,13 +2841,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>94.95276625483082</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>413.3734759809475</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>340.7767994885277</v>
+        <v>342.1496093272373</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>199.4559043409888</v>
+        <v>190.9993129555745</v>
       </c>
       <c r="C32" t="n">
         <v>158.4745782429939</v>
@@ -3045,16 +3045,16 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>8.45659138541424</v>
       </c>
       <c r="J32" t="n">
         <v>377.7382696589756</v>
       </c>
       <c r="K32" t="n">
-        <v>773</v>
+        <v>727.1079320763234</v>
       </c>
       <c r="L32" t="n">
-        <v>351.8156858381969</v>
+        <v>743.0610648197949</v>
       </c>
       <c r="M32" t="n">
         <v>256.9910820920268</v>
@@ -3066,10 +3066,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000421</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>329.9706110579538</v>
+        <v>757.6173000000409</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>81.22967444116941</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
         <v>229.6316114025499</v>
@@ -3221,7 +3221,7 @@
         <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>349.445564079015</v>
+        <v>298.1276103624053</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -3285,19 +3285,19 @@
         <v>8.45659138541424</v>
       </c>
       <c r="J35" t="n">
-        <v>727.7651521517356</v>
+        <v>377.7382696589829</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320760064</v>
+        <v>56.12488247690044</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>727.1079320762534</v>
       </c>
       <c r="M35" t="n">
-        <v>304.6719533611843</v>
+        <v>773.0000000000493</v>
       </c>
       <c r="N35" t="n">
-        <v>153.5855355810966</v>
+        <v>752.1594889580788</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -3452,19 +3452,19 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>109.2047614405202</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P37" t="n">
-        <v>396.4478973282775</v>
+        <v>361.4147497128542</v>
       </c>
       <c r="Q37" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3525,28 +3525,28 @@
         <v>757.6173000000554</v>
       </c>
       <c r="K38" t="n">
-        <v>10.23281455291149</v>
+        <v>10.23281455287789</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M38" t="n">
-        <v>256.9910820920413</v>
+        <v>372.2804586170391</v>
       </c>
       <c r="N38" t="n">
-        <v>153.5855355811038</v>
+        <v>773.0000000000566</v>
       </c>
       <c r="O38" t="n">
-        <v>322.4398520018075</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>757.6173000000553</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>757.6173000000553</v>
+        <v>329.9706110579683</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S38" t="n">
         <v>203.8481678023229</v>
@@ -3555,7 +3555,7 @@
         <v>295.6755817285639</v>
       </c>
       <c r="U38" t="n">
-        <v>366.6778879340249</v>
+        <v>358.2212965486107</v>
       </c>
       <c r="V38" t="n">
         <v>338.8510241668239</v>
@@ -3698,16 +3698,16 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>70.05053078764654</v>
       </c>
       <c r="Q40" t="n">
-        <v>433.5163175103893</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R40" t="n">
         <v>435.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3738,10 +3738,10 @@
         <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>236.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>197.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>191.3632896068686</v>
@@ -3750,7 +3750,7 @@
         <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>190.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>195.0096587035274</v>
@@ -3786,25 +3786,25 @@
         <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
-        <v>281.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>94.47807443345583</v>
+        <v>373.6755817285639</v>
       </c>
       <c r="U41" t="n">
         <v>436.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>416.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>425.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>379.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>298.3174326828064</v>
+        <v>83.31469931210914</v>
       </c>
     </row>
     <row r="42">
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>196.8073545500588</v>
+        <v>334.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>253.5639999646113</v>
@@ -3877,7 +3877,7 @@
         <v>201.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>219.3731429098285</v>
+        <v>81.90670016750896</v>
       </c>
       <c r="X42" t="n">
         <v>206.8627394453875</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>294.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>262.4745782429939</v>
+        <v>142.4109888009625</v>
       </c>
       <c r="D44" t="n">
-        <v>223.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>217.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>217.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>221.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,16 +4020,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>399.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>344.2408432125964</v>
+        <v>462.2212965486107</v>
       </c>
       <c r="V44" t="n">
         <v>442.8510241668239</v>
@@ -4038,7 +4038,7 @@
         <v>451.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>405.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>324.3174326828064</v>
@@ -4066,10 +4066,10 @@
         <v>152.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>138.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>145.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>30.12638589134853</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>16.55705513387049</v>
+        <v>346.3952079728637</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>41.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
         <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
-        <v>39.37280983870968</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>954.8509932204727</v>
+        <v>1510.488528253487</v>
       </c>
       <c r="C2" t="n">
-        <v>904.876671762903</v>
+        <v>1460.514206795918</v>
       </c>
       <c r="D2" t="n">
-        <v>894.4330801064891</v>
+        <v>1450.070615139504</v>
       </c>
       <c r="E2" t="n">
-        <v>890.0257168672279</v>
+        <v>1041.622847859838</v>
       </c>
       <c r="F2" t="n">
-        <v>885.0866979702462</v>
+        <v>1036.683828962857</v>
       </c>
       <c r="G2" t="n">
-        <v>477.2509683874014</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H2" t="n">
-        <v>65.12</v>
+        <v>216.7171309926107</v>
       </c>
       <c r="I2" t="n">
         <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>448.0120508495621</v>
+        <v>65.12</v>
       </c>
       <c r="K2" t="n">
-        <v>1155.766108953703</v>
+        <v>772.8740581041409</v>
       </c>
       <c r="L2" t="n">
-        <v>1961.626108953703</v>
+        <v>1578.734058104141</v>
       </c>
       <c r="M2" t="n">
-        <v>2466.485015931496</v>
+        <v>2083.592965081934</v>
       </c>
       <c r="N2" t="n">
-        <v>2857.58223339183</v>
+        <v>2067.230742859711</v>
       </c>
       <c r="O2" t="n">
-        <v>2841.220011169607</v>
+        <v>2873.090742859712</v>
       </c>
       <c r="P2" t="n">
-        <v>2824.857788947385</v>
+        <v>3256</v>
       </c>
       <c r="Q2" t="n">
         <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3002.587273910814</v>
+        <v>3256</v>
       </c>
       <c r="S2" t="n">
-        <v>2661.638829103296</v>
+        <v>2813.235960095906</v>
       </c>
       <c r="T2" t="n">
-        <v>2473.07763543808</v>
+        <v>2624.67476643069</v>
       </c>
       <c r="U2" t="n">
-        <v>2221.338952055645</v>
+        <v>2372.936083048255</v>
       </c>
       <c r="V2" t="n">
-        <v>1585.12579633158</v>
+        <v>2140.763331364595</v>
       </c>
       <c r="W2" t="n">
-        <v>1344.344507461936</v>
+        <v>1899.982042494951</v>
       </c>
       <c r="X2" t="n">
-        <v>1150.120433259241</v>
+        <v>1705.757968292256</v>
       </c>
       <c r="Y2" t="n">
-        <v>1037.678582064487</v>
+        <v>1593.316117097502</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2100.567579631464</v>
+        <v>931.509519579215</v>
       </c>
       <c r="C3" t="n">
-        <v>2100.567579631464</v>
+        <v>931.509519579215</v>
       </c>
       <c r="D3" t="n">
-        <v>2100.567579631464</v>
+        <v>613.4694159256323</v>
       </c>
       <c r="E3" t="n">
-        <v>2100.567579631464</v>
+        <v>613.4694159256323</v>
       </c>
       <c r="F3" t="n">
-        <v>2100.567579631464</v>
+        <v>613.4694159256323</v>
       </c>
       <c r="G3" t="n">
-        <v>2100.567579631464</v>
+        <v>284.4395817084329</v>
       </c>
       <c r="H3" t="n">
-        <v>2100.567579631464</v>
+        <v>284.4395817084329</v>
       </c>
       <c r="I3" t="n">
-        <v>2100.567579631464</v>
+        <v>65.12</v>
       </c>
       <c r="J3" t="n">
-        <v>2224.524099806763</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K3" t="n">
-        <v>2413.716915901147</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L3" t="n">
-        <v>2685.067377496347</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M3" t="n">
-        <v>2771.147919239206</v>
+        <v>735.7003396077417</v>
       </c>
       <c r="N3" t="n">
-        <v>2904.428203846775</v>
+        <v>868.9806242153101</v>
       </c>
       <c r="O3" t="n">
-        <v>3143.470655530493</v>
+        <v>1108.023075899029</v>
       </c>
       <c r="P3" t="n">
-        <v>3256</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>3256</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>2703.198184553152</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>2231.921416912131</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T3" t="n">
-        <v>2226.509532854036</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U3" t="n">
-        <v>2226.297048247786</v>
+        <v>998.9302766971304</v>
       </c>
       <c r="V3" t="n">
-        <v>2153.331097161986</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W3" t="n">
-        <v>2120.630952808624</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X3" t="n">
-        <v>2100.567579631464</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y3" t="n">
-        <v>2100.567579631464</v>
+        <v>931.509519579215</v>
       </c>
     </row>
     <row r="4">
@@ -4455,37 +4455,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>907.7094380368878</v>
+        <v>594.9714115769964</v>
       </c>
       <c r="C4" t="n">
-        <v>907.7094380368878</v>
+        <v>594.9714115769964</v>
       </c>
       <c r="D4" t="n">
-        <v>907.7094380368878</v>
+        <v>708.2905557019965</v>
       </c>
       <c r="E4" t="n">
-        <v>907.7094380368878</v>
+        <v>826.1194599134095</v>
       </c>
       <c r="F4" t="n">
-        <v>907.7094380368878</v>
+        <v>950.480432505345</v>
       </c>
       <c r="G4" t="n">
-        <v>1045.408215898787</v>
+        <v>1103.88699839223</v>
       </c>
       <c r="H4" t="n">
-        <v>1214.924801058184</v>
+        <v>1273.403583551628</v>
       </c>
       <c r="I4" t="n">
-        <v>1436.057679994267</v>
+        <v>1273.403583551628</v>
       </c>
       <c r="J4" t="n">
-        <v>1436.057679994267</v>
+        <v>1546.422113931143</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931136</v>
+        <v>1546.422113931143</v>
       </c>
       <c r="L4" t="n">
-        <v>1546.422113931136</v>
+        <v>1546.422113931143</v>
       </c>
       <c r="M4" t="n">
         <v>1430.29164756134</v>
@@ -4506,25 +4506,25 @@
         <v>65.12</v>
       </c>
       <c r="S4" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T4" t="n">
-        <v>290.445934252978</v>
+        <v>65.12</v>
       </c>
       <c r="U4" t="n">
-        <v>536.9971268912645</v>
+        <v>311.6711926382866</v>
       </c>
       <c r="V4" t="n">
-        <v>735.8185197772104</v>
+        <v>311.6711926382866</v>
       </c>
       <c r="W4" t="n">
-        <v>907.7094380368878</v>
+        <v>483.5621108979641</v>
       </c>
       <c r="X4" t="n">
-        <v>907.7094380368878</v>
+        <v>483.5621108979641</v>
       </c>
       <c r="Y4" t="n">
-        <v>907.7094380368878</v>
+        <v>594.9714115769964</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1106.448124213083</v>
+        <v>702.4077201726793</v>
       </c>
       <c r="C5" t="n">
-        <v>1056.473802755514</v>
+        <v>652.4333987151097</v>
       </c>
       <c r="D5" t="n">
-        <v>1046.0302110991</v>
+        <v>641.9898070586958</v>
       </c>
       <c r="E5" t="n">
-        <v>1041.622847859838</v>
+        <v>637.5824438194345</v>
       </c>
       <c r="F5" t="n">
-        <v>1036.683828962857</v>
+        <v>632.6434249224528</v>
       </c>
       <c r="G5" t="n">
-        <v>628.8480993800122</v>
+        <v>224.8076953396081</v>
       </c>
       <c r="H5" t="n">
         <v>216.7171309926107</v>
@@ -4564,28 +4564,28 @@
         <v>1155.766108953703</v>
       </c>
       <c r="L5" t="n">
-        <v>1961.626108953703</v>
+        <v>1139.40388673148</v>
       </c>
       <c r="M5" t="n">
-        <v>1945.263886731481</v>
+        <v>1644.262793709273</v>
       </c>
       <c r="N5" t="n">
-        <v>1928.901664509258</v>
+        <v>2035.360011169608</v>
       </c>
       <c r="O5" t="n">
-        <v>2734.761664509258</v>
+        <v>2018.997788947385</v>
       </c>
       <c r="P5" t="n">
-        <v>3256</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q5" t="n">
         <v>3256</v>
       </c>
       <c r="R5" t="n">
-        <v>3002.587273910814</v>
+        <v>3256</v>
       </c>
       <c r="S5" t="n">
-        <v>2502.740639767053</v>
+        <v>2756.153365856239</v>
       </c>
       <c r="T5" t="n">
         <v>2220.634362390286</v>
@@ -4603,7 +4603,7 @@
         <v>1301.717564251852</v>
       </c>
       <c r="Y5" t="n">
-        <v>1189.275713057098</v>
+        <v>785.2353090166939</v>
       </c>
     </row>
     <row r="6">
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>737.2167456696003</v>
+        <v>65.12</v>
       </c>
       <c r="C6" t="n">
-        <v>737.2167456696003</v>
+        <v>65.12</v>
       </c>
       <c r="D6" t="n">
-        <v>737.2167456696003</v>
+        <v>65.12</v>
       </c>
       <c r="E6" t="n">
-        <v>737.2167456696003</v>
+        <v>65.12</v>
       </c>
       <c r="F6" t="n">
-        <v>394.1498342171994</v>
+        <v>65.12</v>
       </c>
       <c r="G6" t="n">
         <v>65.12</v>
@@ -4670,19 +4670,19 @@
         <v>999.1427613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>998.9302766971304</v>
+        <v>594.8898726567263</v>
       </c>
       <c r="V6" t="n">
-        <v>984.2730371097363</v>
+        <v>580.2326330693322</v>
       </c>
       <c r="W6" t="n">
-        <v>951.5728927563741</v>
+        <v>143.492084675566</v>
       </c>
       <c r="X6" t="n">
-        <v>737.2167456696003</v>
+        <v>65.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>737.2167456696003</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>410.490623265121</v>
+        <v>681.7260933634225</v>
       </c>
       <c r="C7" t="n">
-        <v>536.4926290835568</v>
+        <v>807.7280991818583</v>
       </c>
       <c r="D7" t="n">
-        <v>649.8117732085569</v>
+        <v>921.0472433068584</v>
       </c>
       <c r="E7" t="n">
-        <v>767.64067741997</v>
+        <v>921.0472433068584</v>
       </c>
       <c r="F7" t="n">
-        <v>892.0016500119054</v>
+        <v>1045.408215898794</v>
       </c>
       <c r="G7" t="n">
-        <v>1045.408215898791</v>
+        <v>1045.408215898794</v>
       </c>
       <c r="H7" t="n">
-        <v>1214.924801058188</v>
+        <v>1214.924801058192</v>
       </c>
       <c r="I7" t="n">
-        <v>1436.057679994271</v>
+        <v>1436.057679994275</v>
       </c>
       <c r="J7" t="n">
-        <v>1436.057679994271</v>
+        <v>1436.057679994275</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.42211393114</v>
+        <v>1546.422113931143</v>
       </c>
       <c r="L7" t="n">
-        <v>1522.636630943484</v>
+        <v>1522.636630943487</v>
       </c>
       <c r="M7" t="n">
-        <v>1400.786518415656</v>
+        <v>1400.786518415659</v>
       </c>
       <c r="N7" t="n">
-        <v>1227.872300969509</v>
+        <v>1227.872300969512</v>
       </c>
       <c r="O7" t="n">
-        <v>984.9979938189891</v>
+        <v>984.9979938189923</v>
       </c>
       <c r="P7" t="n">
-        <v>694.6465823762846</v>
+        <v>694.6465823762878</v>
       </c>
       <c r="Q7" t="n">
-        <v>365.5160102292159</v>
+        <v>365.5160102292191</v>
       </c>
       <c r="R7" t="n">
         <v>65.12</v>
       </c>
       <c r="S7" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T7" t="n">
-        <v>290.445934252978</v>
+        <v>253.1956791588049</v>
       </c>
       <c r="U7" t="n">
-        <v>410.490623265121</v>
+        <v>253.1956791588049</v>
       </c>
       <c r="V7" t="n">
-        <v>410.490623265121</v>
+        <v>452.0170720447508</v>
       </c>
       <c r="W7" t="n">
-        <v>410.490623265121</v>
+        <v>623.9079903044283</v>
       </c>
       <c r="X7" t="n">
-        <v>410.490623265121</v>
+        <v>623.9079903044283</v>
       </c>
       <c r="Y7" t="n">
-        <v>410.490623265121</v>
+        <v>681.7260933634225</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>645.3251259330118</v>
+        <v>702.4077201726793</v>
       </c>
       <c r="C8" t="n">
-        <v>595.3508044754421</v>
+        <v>652.4333987151097</v>
       </c>
       <c r="D8" t="n">
-        <v>584.9072128190282</v>
+        <v>641.9898070586958</v>
       </c>
       <c r="E8" t="n">
-        <v>580.499849579767</v>
+        <v>637.5824438194345</v>
       </c>
       <c r="F8" t="n">
-        <v>575.5608306827853</v>
+        <v>632.6434249224528</v>
       </c>
       <c r="G8" t="n">
-        <v>571.7655051403447</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H8" t="n">
         <v>216.7171309926107</v>
@@ -4798,19 +4798,19 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>1155.766108953703</v>
+        <v>937.5543724554984</v>
       </c>
       <c r="L8" t="n">
-        <v>1546.863326414032</v>
+        <v>1743.414372455498</v>
       </c>
       <c r="M8" t="n">
-        <v>2051.722233391825</v>
+        <v>2248.273279433291</v>
       </c>
       <c r="N8" t="n">
-        <v>2035.360011169603</v>
+        <v>2857.58223339183</v>
       </c>
       <c r="O8" t="n">
-        <v>2018.997788947385</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P8" t="n">
         <v>2824.857788947385</v>
@@ -4819,28 +4819,28 @@
         <v>3256</v>
       </c>
       <c r="R8" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S8" t="n">
-        <v>2756.153365856239</v>
+        <v>2906.781043807457</v>
       </c>
       <c r="T8" t="n">
-        <v>2163.551768150619</v>
+        <v>2718.219850142241</v>
       </c>
       <c r="U8" t="n">
-        <v>1911.813084768184</v>
+        <v>2466.481166759806</v>
       </c>
       <c r="V8" t="n">
-        <v>1679.640333084523</v>
+        <v>2140.763331364595</v>
       </c>
       <c r="W8" t="n">
-        <v>1438.859044214879</v>
+        <v>1899.982042494951</v>
       </c>
       <c r="X8" t="n">
-        <v>1244.634970012185</v>
+        <v>1301.717564251852</v>
       </c>
       <c r="Y8" t="n">
-        <v>1132.193118817431</v>
+        <v>1189.275713057098</v>
       </c>
     </row>
     <row r="9">
@@ -4856,13 +4856,13 @@
         <v>931.509519579215</v>
       </c>
       <c r="D9" t="n">
-        <v>740.2832657544849</v>
+        <v>754.3203429896864</v>
       </c>
       <c r="E9" t="n">
-        <v>394.1498342171994</v>
+        <v>408.1869114524009</v>
       </c>
       <c r="F9" t="n">
-        <v>394.1498342171994</v>
+        <v>65.12</v>
       </c>
       <c r="G9" t="n">
         <v>65.12</v>
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>410.4906232651221</v>
+        <v>741.9879361380654</v>
       </c>
       <c r="C10" t="n">
-        <v>536.4926290835579</v>
+        <v>867.9899419565012</v>
       </c>
       <c r="D10" t="n">
-        <v>649.811773208558</v>
+        <v>981.3090860815013</v>
       </c>
       <c r="E10" t="n">
-        <v>767.640677419971</v>
+        <v>1099.137990292914</v>
       </c>
       <c r="F10" t="n">
-        <v>892.0016500119065</v>
+        <v>1223.49896288485</v>
       </c>
       <c r="G10" t="n">
-        <v>1045.408215898792</v>
+        <v>1376.905528771735</v>
       </c>
       <c r="H10" t="n">
-        <v>1214.924801058189</v>
+        <v>1546.422113931133</v>
       </c>
       <c r="I10" t="n">
-        <v>1436.057679994272</v>
+        <v>1546.422113931133</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994272</v>
+        <v>1546.422113931133</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931141</v>
+        <v>1546.422113931133</v>
       </c>
       <c r="L10" t="n">
-        <v>1522.636630943485</v>
+        <v>1546.422113931133</v>
       </c>
       <c r="M10" t="n">
-        <v>1400.786518415657</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1227.87230096951</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O10" t="n">
-        <v>984.99799381899</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P10" t="n">
-        <v>694.6465823762856</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>365.5160102292168</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R10" t="n">
         <v>65.12</v>
       </c>
       <c r="S10" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T10" t="n">
-        <v>187.3239849197977</v>
+        <v>65.12</v>
       </c>
       <c r="U10" t="n">
-        <v>187.3239849197977</v>
+        <v>311.6711926382866</v>
       </c>
       <c r="V10" t="n">
-        <v>187.3239849197977</v>
+        <v>510.4925855242326</v>
       </c>
       <c r="W10" t="n">
-        <v>187.3239849197977</v>
+        <v>630.2305984717733</v>
       </c>
       <c r="X10" t="n">
-        <v>187.3239849197977</v>
+        <v>630.2305984717733</v>
       </c>
       <c r="Y10" t="n">
-        <v>298.73328559883</v>
+        <v>630.2305984717733</v>
       </c>
     </row>
     <row r="11">
@@ -5011,13 +5011,13 @@
         <v>417.1649250963513</v>
       </c>
       <c r="C11" t="n">
-        <v>252.3312684240907</v>
+        <v>417.1649250963513</v>
       </c>
       <c r="D11" t="n">
-        <v>65.12</v>
+        <v>417.1649250963513</v>
       </c>
       <c r="E11" t="n">
-        <v>65.12</v>
+        <v>235.9898850894132</v>
       </c>
       <c r="F11" t="n">
         <v>65.12</v>
@@ -5044,13 +5044,13 @@
         <v>2482.844308114459</v>
       </c>
       <c r="N11" t="n">
-        <v>3096.064627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>3256</v>
@@ -5111,22 +5111,22 @@
         <v>72.91487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>215.7971006891144</v>
+        <v>419.6213981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>627.7399167834978</v>
+        <v>831.5642142372474</v>
       </c>
       <c r="L12" t="n">
-        <v>1121.840378378698</v>
+        <v>1325.664675832448</v>
       </c>
       <c r="M12" t="n">
-        <v>1430.670920121557</v>
+        <v>1634.495217575307</v>
       </c>
       <c r="N12" t="n">
-        <v>1786.701204729125</v>
+        <v>1990.525502182875</v>
       </c>
       <c r="O12" t="n">
-        <v>2248.493656412844</v>
+        <v>2452.317953866594</v>
       </c>
       <c r="P12" t="n">
         <v>2583.773000882351</v>
@@ -5208,10 +5208,10 @@
         <v>409.3389893823512</v>
       </c>
       <c r="P13" t="n">
-        <v>65.12</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.12</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="R13" t="n">
         <v>65.12</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>891.2048733179198</v>
+        <v>653.4059340138207</v>
       </c>
       <c r="C14" t="n">
-        <v>690.7255013552997</v>
+        <v>452.9265620512006</v>
       </c>
       <c r="D14" t="n">
-        <v>529.7768591938352</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="E14" t="n">
-        <v>374.8644454495234</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="F14" t="n">
-        <v>219.4203760474911</v>
+        <v>223.7156148520479</v>
       </c>
       <c r="G14" t="n">
-        <v>65.12</v>
+        <v>223.7156148520479</v>
       </c>
       <c r="H14" t="n">
         <v>65.12</v>
@@ -5272,19 +5272,19 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>1166.135479385524</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>1971.995479385524</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="M14" t="n">
-        <v>1971.995479385524</v>
+        <v>967.2779417665907</v>
       </c>
       <c r="N14" t="n">
-        <v>2585.215799160287</v>
+        <v>1580.498261541354</v>
       </c>
       <c r="O14" t="n">
-        <v>2817.400904947332</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="P14" t="n">
         <v>2817.400904947332</v>
@@ -5296,25 +5296,25 @@
         <v>3256</v>
       </c>
       <c r="S14" t="n">
-        <v>3247.487658695693</v>
+        <v>3009.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>2908.421414525426</v>
+        <v>2670.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>2506.17768063794</v>
+        <v>2268.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>2123.499878449229</v>
+        <v>1885.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>1732.213539074535</v>
+        <v>1494.414599770435</v>
       </c>
       <c r="X14" t="n">
-        <v>1387.48441436679</v>
+        <v>1149.68547506269</v>
       </c>
       <c r="Y14" t="n">
-        <v>1124.537512666985</v>
+        <v>886.7385733628859</v>
       </c>
     </row>
     <row r="15">
@@ -5351,16 +5351,16 @@
         <v>471.1013981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>824.8305228441038</v>
+        <v>908.7842142372473</v>
       </c>
       <c r="L15" t="n">
-        <v>1344.670984439304</v>
+        <v>1428.624675832447</v>
       </c>
       <c r="M15" t="n">
-        <v>1430.751526182163</v>
+        <v>1679.241526182163</v>
       </c>
       <c r="N15" t="n">
-        <v>1564.031810789731</v>
+        <v>1812.521810789732</v>
       </c>
       <c r="O15" t="n">
         <v>2051.564262473451</v>
@@ -5442,13 +5442,13 @@
         <v>599.0397446017254</v>
       </c>
       <c r="O16" t="n">
-        <v>599.0397446017254</v>
+        <v>505.9764619477551</v>
       </c>
       <c r="P16" t="n">
-        <v>599.0397446017254</v>
+        <v>65.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>545.5261898799506</v>
+        <v>65.12</v>
       </c>
       <c r="R16" t="n">
         <v>65.12</v>
@@ -5494,7 +5494,7 @@
         <v>448.1766172565348</v>
       </c>
       <c r="F17" t="n">
-        <v>321.0153761373309</v>
+        <v>321.4503343338824</v>
       </c>
       <c r="G17" t="n">
         <v>195.4327865692196</v>
@@ -5518,13 +5518,13 @@
         <v>1676.984308114459</v>
       </c>
       <c r="N17" t="n">
-        <v>1676.984308114459</v>
+        <v>2290.204627889222</v>
       </c>
       <c r="O17" t="n">
-        <v>2011.540904947332</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="P17" t="n">
-        <v>2817.400904947332</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="Q17" t="n">
         <v>3256</v>
@@ -5582,22 +5582,22 @@
         <v>65.12</v>
       </c>
       <c r="I18" t="n">
-        <v>65.12</v>
+        <v>126.374877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>189.076520175299</v>
+        <v>526.5413981428638</v>
       </c>
       <c r="K18" t="n">
-        <v>378.2693362696824</v>
+        <v>869.8480986016793</v>
       </c>
       <c r="L18" t="n">
-        <v>864.9885601968793</v>
+        <v>1141.198560196879</v>
       </c>
       <c r="M18" t="n">
-        <v>951.0691019397386</v>
+        <v>1227.279101939739</v>
       </c>
       <c r="N18" t="n">
-        <v>1084.349386547307</v>
+        <v>1360.559386547307</v>
       </c>
       <c r="O18" t="n">
         <v>1599.601838231026</v>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>879.6685602764463</v>
+        <v>880.1035184729978</v>
       </c>
       <c r="C20" t="n">
-        <v>707.4720165966545</v>
+        <v>707.906974793206</v>
       </c>
       <c r="D20" t="n">
-        <v>574.8062027180183</v>
+        <v>575.2411609145698</v>
       </c>
       <c r="E20" t="n">
-        <v>448.1766172565348</v>
+        <v>448.6115754530863</v>
       </c>
       <c r="F20" t="n">
         <v>321.4503343338824</v>
@@ -5746,22 +5746,22 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>1166.135479385524</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>1971.995479385524</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="M20" t="n">
-        <v>2482.844308114459</v>
+        <v>967.2779417665907</v>
       </c>
       <c r="N20" t="n">
-        <v>3096.064627889222</v>
+        <v>1580.498261541354</v>
       </c>
       <c r="O20" t="n">
-        <v>3096.064627889222</v>
+        <v>2386.358261541354</v>
       </c>
       <c r="P20" t="n">
-        <v>3096.064627889222</v>
+        <v>3192.218261541354</v>
       </c>
       <c r="Q20" t="n">
         <v>3256</v>
@@ -5770,25 +5770,25 @@
         <v>3256</v>
       </c>
       <c r="S20" t="n">
-        <v>3037.971547674421</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.623089983534</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.662184378877</v>
       </c>
       <c r="V20" t="n">
-        <v>1998.832252276443</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W20" t="n">
-        <v>1635.828741184576</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X20" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y20" t="n">
-        <v>1084.718371342683</v>
+        <v>1085.153329539235</v>
       </c>
     </row>
     <row r="21">
@@ -5825,22 +5825,22 @@
         <v>526.5413981428638</v>
       </c>
       <c r="K21" t="n">
-        <v>974.7096261621045</v>
+        <v>715.7342142372472</v>
       </c>
       <c r="L21" t="n">
-        <v>1246.060087757305</v>
+        <v>987.0846758324474</v>
       </c>
       <c r="M21" t="n">
-        <v>1332.140629500164</v>
+        <v>1073.165217575307</v>
       </c>
       <c r="N21" t="n">
-        <v>1465.420914107732</v>
+        <v>1206.445502182875</v>
       </c>
       <c r="O21" t="n">
-        <v>1704.463365791451</v>
+        <v>1445.487953866594</v>
       </c>
       <c r="P21" t="n">
-        <v>1816.992710260958</v>
+        <v>1712.131182700533</v>
       </c>
       <c r="Q21" t="n">
         <v>1816.992710260958</v>
@@ -5877,52 +5877,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>414.3442160506673</v>
+        <v>422.5399739669084</v>
       </c>
       <c r="C22" t="n">
-        <v>420.5562218691031</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="D22" t="n">
-        <v>420.5562218691031</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="E22" t="n">
-        <v>420.5562218691031</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="F22" t="n">
-        <v>425.1271944610386</v>
+        <v>433.3229523772797</v>
       </c>
       <c r="G22" t="n">
-        <v>458.7437603479239</v>
+        <v>466.939518264165</v>
       </c>
       <c r="H22" t="n">
-        <v>508.4703455073215</v>
+        <v>516.6661034235625</v>
       </c>
       <c r="I22" t="n">
-        <v>609.8132244434044</v>
+        <v>618.0089823596454</v>
       </c>
       <c r="J22" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="K22" t="n">
-        <v>851.1069650958557</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="L22" t="n">
-        <v>705.0992598859777</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="M22" t="n">
-        <v>477.6936336649268</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="N22" t="n">
-        <v>477.6936336649268</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O22" t="n">
-        <v>477.6936336649268</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P22" t="n">
-        <v>65.12</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q22" t="n">
-        <v>65.12</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R22" t="n">
         <v>65.12</v>
@@ -5983,16 +5983,16 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>1166.135479385524</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1971.995479385524</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>2011.540904947332</v>
+        <v>967.2779417665907</v>
       </c>
       <c r="N23" t="n">
-        <v>2011.540904947332</v>
+        <v>1580.498261541354</v>
       </c>
       <c r="O23" t="n">
         <v>2011.540904947332</v>
@@ -6004,7 +6004,7 @@
         <v>3256</v>
       </c>
       <c r="R23" t="n">
-        <v>3256.000000000069</v>
+        <v>3256</v>
       </c>
       <c r="S23" t="n">
         <v>3038.406505870973</v>
@@ -6059,25 +6059,25 @@
         <v>126.374877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>250.3313981428639</v>
+        <v>526.5413981428638</v>
       </c>
       <c r="K24" t="n">
-        <v>715.7342142372473</v>
+        <v>974.7096261621045</v>
       </c>
       <c r="L24" t="n">
-        <v>987.0846758324474</v>
+        <v>1246.060087757305</v>
       </c>
       <c r="M24" t="n">
-        <v>1073.165217575307</v>
+        <v>1332.140629500164</v>
       </c>
       <c r="N24" t="n">
-        <v>1206.445502182875</v>
+        <v>1465.420914107732</v>
       </c>
       <c r="O24" t="n">
-        <v>1599.601838231026</v>
+        <v>1704.463365791451</v>
       </c>
       <c r="P24" t="n">
-        <v>1712.131182700533</v>
+        <v>1816.992710260958</v>
       </c>
       <c r="Q24" t="n">
         <v>1816.992710260958</v>
@@ -6153,13 +6153,13 @@
         <v>859.3027230120967</v>
       </c>
       <c r="O25" t="n">
-        <v>494.2061936393544</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P25" t="n">
-        <v>81.63255997442758</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q25" t="n">
-        <v>65.12</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R25" t="n">
         <v>65.12</v>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1022.921205738787</v>
+        <v>796.1792075135407</v>
       </c>
       <c r="C26" t="n">
         <v>796.1792075135407</v>
@@ -6220,19 +6220,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>1162.855479385524</v>
+        <v>764.0617564436071</v>
       </c>
       <c r="L26" t="n">
-        <v>1928.125479385524</v>
+        <v>764.0617564436071</v>
       </c>
       <c r="M26" t="n">
-        <v>2040.180585172569</v>
+        <v>1274.910585172542</v>
       </c>
       <c r="N26" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947305</v>
       </c>
       <c r="O26" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947305</v>
       </c>
       <c r="P26" t="n">
         <v>2653.400904947332</v>
@@ -6241,28 +6241,28 @@
         <v>3092</v>
       </c>
       <c r="R26" t="n">
-        <v>3065.860001183541</v>
+        <v>3092</v>
       </c>
       <c r="S26" t="n">
-        <v>2793.286094312508</v>
+        <v>2819.426093128967</v>
       </c>
       <c r="T26" t="n">
-        <v>2788.773076070714</v>
+        <v>2454.097222696074</v>
       </c>
       <c r="U26" t="n">
-        <v>2360.266715920602</v>
+        <v>2025.590862545962</v>
       </c>
       <c r="V26" t="n">
-        <v>2360.266715920602</v>
+        <v>1616.650434094625</v>
       </c>
       <c r="W26" t="n">
-        <v>1942.717750283281</v>
+        <v>1199.101468457304</v>
       </c>
       <c r="X26" t="n">
-        <v>1571.725999312909</v>
+        <v>828.1097174869326</v>
       </c>
       <c r="Y26" t="n">
-        <v>1282.516471350479</v>
+        <v>796.1792075135407</v>
       </c>
     </row>
     <row r="27">
@@ -6302,10 +6302,10 @@
         <v>828.2842142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1322.384675832448</v>
+        <v>1118.560378378698</v>
       </c>
       <c r="M27" t="n">
-        <v>1631.215217575307</v>
+        <v>1427.390920121557</v>
       </c>
       <c r="N27" t="n">
         <v>1783.421204729126</v>
@@ -6387,10 +6387,10 @@
         <v>406.0589893823512</v>
       </c>
       <c r="N28" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="O28" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="P28" t="n">
         <v>61.84</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1204.096245745725</v>
+        <v>954.2451921174961</v>
       </c>
       <c r="C29" t="n">
-        <v>977.3542475204788</v>
+        <v>727.5031938922498</v>
       </c>
       <c r="D29" t="n">
-        <v>790.1429790963881</v>
+        <v>540.2919254681591</v>
       </c>
       <c r="E29" t="n">
-        <v>608.9679390894501</v>
+        <v>359.116885461221</v>
       </c>
       <c r="F29" t="n">
-        <v>427.2612434247916</v>
+        <v>177.4101897965626</v>
       </c>
       <c r="G29" t="n">
-        <v>246.6982411146742</v>
+        <v>61.84</v>
       </c>
       <c r="H29" t="n">
         <v>61.84</v>
@@ -6460,19 +6460,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="L29" t="n">
-        <v>1218.419113037656</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="M29" t="n">
-        <v>1218.419113037656</v>
+        <v>509.6405851725002</v>
       </c>
       <c r="N29" t="n">
-        <v>1561.459999999931</v>
+        <v>1122.860904947263</v>
       </c>
       <c r="O29" t="n">
-        <v>2326.729999999965</v>
+        <v>1888.130904947298</v>
       </c>
       <c r="P29" t="n">
-        <v>3092</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>3092</v>
@@ -6484,22 +6484,22 @@
         <v>3065.860001183541</v>
       </c>
       <c r="T29" t="n">
-        <v>3065.860001183541</v>
+        <v>2700.531130750648</v>
       </c>
       <c r="U29" t="n">
-        <v>2637.353641033429</v>
+        <v>2700.531130750648</v>
       </c>
       <c r="V29" t="n">
-        <v>2541.441755927539</v>
+        <v>2291.590702299311</v>
       </c>
       <c r="W29" t="n">
-        <v>2123.892790290219</v>
+        <v>1874.04173666199</v>
       </c>
       <c r="X29" t="n">
-        <v>1752.901039319847</v>
+        <v>1503.049985691618</v>
       </c>
       <c r="Y29" t="n">
-        <v>1463.691511357417</v>
+        <v>1213.840457729188</v>
       </c>
     </row>
     <row r="30">
@@ -6530,25 +6530,25 @@
         <v>61.84</v>
       </c>
       <c r="I30" t="n">
-        <v>61.84</v>
+        <v>69.63487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>408.546520175299</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>820.4893362696823</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L30" t="n">
-        <v>1314.589797864882</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M30" t="n">
-        <v>1623.420339607742</v>
+        <v>1631.215217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1979.45062421531</v>
+        <v>1987.245502182875</v>
       </c>
       <c r="O30" t="n">
-        <v>2441.243075899029</v>
+        <v>2245.213656412845</v>
       </c>
       <c r="P30" t="n">
         <v>2580.493000882351</v>
@@ -6588,52 +6588,52 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="C31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="D31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="E31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="F31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="G31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="H31" t="n">
-        <v>170.342369793817</v>
+        <v>171.7290463985742</v>
       </c>
       <c r="I31" t="n">
-        <v>218.2252487298999</v>
+        <v>219.6119253346571</v>
       </c>
       <c r="J31" t="n">
-        <v>406.0589893823512</v>
+        <v>407.4456659871084</v>
       </c>
       <c r="K31" t="n">
-        <v>406.0589893823512</v>
+        <v>407.4456659871084</v>
       </c>
       <c r="L31" t="n">
-        <v>406.0589893823512</v>
+        <v>407.4456659871084</v>
       </c>
       <c r="M31" t="n">
-        <v>406.0589893823512</v>
+        <v>407.4456659871084</v>
       </c>
       <c r="N31" t="n">
-        <v>406.0589893823512</v>
+        <v>407.4456659871084</v>
       </c>
       <c r="O31" t="n">
-        <v>406.0589893823512</v>
+        <v>407.4456659871084</v>
       </c>
       <c r="P31" t="n">
-        <v>406.0589893823512</v>
+        <v>407.4456659871084</v>
       </c>
       <c r="Q31" t="n">
-        <v>406.0589893823512</v>
+        <v>407.4456659871084</v>
       </c>
       <c r="R31" t="n">
         <v>61.84</v>
@@ -6651,13 +6651,13 @@
         <v>175.5382646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="X31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="Y31" t="n">
-        <v>174.1515880782802</v>
+        <v>175.5382646830375</v>
       </c>
     </row>
     <row r="32">
@@ -6667,25 +6667,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>804.0962457457251</v>
+        <v>812.6382572461436</v>
       </c>
       <c r="C32" t="n">
-        <v>644.0209141871454</v>
+        <v>652.5629256875638</v>
       </c>
       <c r="D32" t="n">
-        <v>523.4763124297214</v>
+        <v>532.0183239301398</v>
       </c>
       <c r="E32" t="n">
-        <v>408.96793908945</v>
+        <v>417.5099505898684</v>
       </c>
       <c r="F32" t="n">
-        <v>293.9279100914582</v>
+        <v>302.4699215918766</v>
       </c>
       <c r="G32" t="n">
-        <v>180.0315744480075</v>
+        <v>188.5735859484259</v>
       </c>
       <c r="H32" t="n">
-        <v>61.84</v>
+        <v>70.38201150041843</v>
       </c>
       <c r="I32" t="n">
         <v>61.84</v>
@@ -6694,22 +6694,22 @@
         <v>445.5561922637025</v>
       </c>
       <c r="K32" t="n">
-        <v>430.0181114556216</v>
+        <v>430.9405883765116</v>
       </c>
       <c r="L32" t="n">
-        <v>794.4855845766731</v>
+        <v>445.6438562353047</v>
       </c>
       <c r="M32" t="n">
-        <v>1300.168632968607</v>
+        <v>951.3269046272384</v>
       </c>
       <c r="N32" t="n">
-        <v>1910.301728341285</v>
+        <v>1561.459999999917</v>
       </c>
       <c r="O32" t="n">
-        <v>2675.571728341327</v>
+        <v>2326.729999999959</v>
       </c>
       <c r="P32" t="n">
-        <v>2660.033647533245</v>
+        <v>3092</v>
       </c>
       <c r="Q32" t="n">
         <v>3092</v>
@@ -6767,19 +6767,19 @@
         <v>61.84</v>
       </c>
       <c r="I33" t="n">
-        <v>71.63058051381563</v>
+        <v>134.974877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>195.5871006891146</v>
+        <v>483.6771006891146</v>
       </c>
       <c r="K33" t="n">
-        <v>384.779916783498</v>
+        <v>672.869916783498</v>
       </c>
       <c r="L33" t="n">
-        <v>656.1303783786981</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M33" t="n">
-        <v>742.2109201215574</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N33" t="n">
         <v>1163.581204729126</v>
@@ -6855,13 +6855,13 @@
         <v>1011.831843630726</v>
       </c>
       <c r="L34" t="n">
-        <v>929.781667427525</v>
+        <v>877.9453505420606</v>
       </c>
       <c r="M34" t="n">
-        <v>697.8305447986868</v>
+        <v>645.9942279132224</v>
       </c>
       <c r="N34" t="n">
-        <v>414.8153172515302</v>
+        <v>362.9790003660659</v>
       </c>
       <c r="O34" t="n">
         <v>61.84</v>
@@ -6928,16 +6928,16 @@
         <v>61.84</v>
       </c>
       <c r="J35" t="n">
-        <v>91.99368469526542</v>
+        <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>77.37808080808094</v>
+        <v>1154.134391781985</v>
       </c>
       <c r="L35" t="n">
-        <v>61.84</v>
+        <v>1139.518787894795</v>
       </c>
       <c r="M35" t="n">
-        <v>519.3605521604688</v>
+        <v>1123.980707086714</v>
       </c>
       <c r="N35" t="n">
         <v>1129.493647533147</v>
@@ -7007,25 +7007,25 @@
         <v>134.974877967565</v>
       </c>
       <c r="J36" t="n">
-        <v>547.0213981428639</v>
+        <v>483.6771006891146</v>
       </c>
       <c r="K36" t="n">
-        <v>736.2142142372472</v>
+        <v>672.869916783498</v>
       </c>
       <c r="L36" t="n">
-        <v>1007.564675832447</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M36" t="n">
-        <v>1093.645217575307</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N36" t="n">
-        <v>1226.925502182875</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O36" t="n">
-        <v>1465.967953866594</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P36" t="n">
-        <v>1578.4972983361</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q36" t="n">
         <v>1631.894528442776</v>
@@ -7062,49 +7062,49 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>486.0066123122328</v>
+        <v>486.0066123122566</v>
       </c>
       <c r="C37" t="n">
-        <v>504.0986181306686</v>
+        <v>504.0986181306923</v>
       </c>
       <c r="D37" t="n">
-        <v>509.5077622556687</v>
+        <v>509.5077622556924</v>
       </c>
       <c r="E37" t="n">
-        <v>519.4266664670818</v>
+        <v>519.4266664671054</v>
       </c>
       <c r="F37" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590409</v>
       </c>
       <c r="G37" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459262</v>
       </c>
       <c r="H37" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053238</v>
       </c>
       <c r="I37" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414067</v>
       </c>
       <c r="J37" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693858</v>
       </c>
       <c r="K37" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="L37" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="M37" t="n">
-        <v>1011.831843630703</v>
+        <v>779.8807210018881</v>
       </c>
       <c r="N37" t="n">
-        <v>1011.831843630703</v>
+        <v>779.8807210018881</v>
       </c>
       <c r="O37" t="n">
-        <v>901.5240037917935</v>
+        <v>426.9054037503578</v>
       </c>
       <c r="P37" t="n">
-        <v>501.0715822480788</v>
+        <v>61.84</v>
       </c>
       <c r="Q37" t="n">
         <v>61.84</v>
@@ -7168,34 +7168,34 @@
         <v>61.84</v>
       </c>
       <c r="K38" t="n">
-        <v>771.3406764391785</v>
+        <v>771.3406764391792</v>
       </c>
       <c r="L38" t="n">
-        <v>1536.610676439178</v>
+        <v>755.8025956310983</v>
       </c>
       <c r="M38" t="n">
-        <v>2042.293724831112</v>
+        <v>1145.031728341216</v>
       </c>
       <c r="N38" t="n">
-        <v>2652.42682020379</v>
+        <v>1129.493647533134</v>
       </c>
       <c r="O38" t="n">
-        <v>3092</v>
+        <v>1894.76364753319</v>
       </c>
       <c r="P38" t="n">
-        <v>3092</v>
+        <v>2660.033647533246</v>
       </c>
       <c r="Q38" t="n">
         <v>3092</v>
       </c>
       <c r="R38" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S38" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T38" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U38" t="n">
         <v>2217.048851045543</v>
@@ -7241,16 +7241,16 @@
         <v>61.84</v>
       </c>
       <c r="I39" t="n">
-        <v>134.974877967565</v>
+        <v>71.63058051381552</v>
       </c>
       <c r="J39" t="n">
-        <v>258.9313981428639</v>
+        <v>195.5871006891145</v>
       </c>
       <c r="K39" t="n">
-        <v>448.1242142372473</v>
+        <v>384.7799167834979</v>
       </c>
       <c r="L39" t="n">
-        <v>719.4746758324475</v>
+        <v>656.130378378698</v>
       </c>
       <c r="M39" t="n">
         <v>1030.300920121557</v>
@@ -7341,13 +7341,13 @@
         <v>1011.831843630703</v>
       </c>
       <c r="P40" t="n">
-        <v>1011.831843630703</v>
+        <v>941.0737317239891</v>
       </c>
       <c r="Q40" t="n">
-        <v>573.9365734181883</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R40" t="n">
-        <v>133.9344239422782</v>
+        <v>61.84</v>
       </c>
       <c r="S40" t="n">
         <v>61.84</v>
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1276.823518472998</v>
+        <v>645.943613149907</v>
       </c>
       <c r="C41" t="n">
-        <v>1037.960308126539</v>
+        <v>645.943613149907</v>
       </c>
       <c r="D41" t="n">
-        <v>838.6278275812365</v>
+        <v>645.943613149907</v>
       </c>
       <c r="E41" t="n">
-        <v>645.3315754530863</v>
+        <v>452.6473610217569</v>
       </c>
       <c r="F41" t="n">
-        <v>451.5036676672158</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="G41" t="n">
         <v>258.8194532358863</v>
@@ -7402,25 +7402,25 @@
         <v>61.84</v>
       </c>
       <c r="J41" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K41" t="n">
-        <v>61.84</v>
+        <v>1050.611171270938</v>
       </c>
       <c r="L41" t="n">
-        <v>764.0617564435712</v>
+        <v>1050.611171270938</v>
       </c>
       <c r="M41" t="n">
-        <v>1274.910585172506</v>
+        <v>1561.459999999874</v>
       </c>
       <c r="N41" t="n">
-        <v>1888.130904947269</v>
+        <v>1561.459999999874</v>
       </c>
       <c r="O41" t="n">
-        <v>2653.400904947332</v>
+        <v>2326.729999999937</v>
       </c>
       <c r="P41" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q41" t="n">
         <v>3092</v>
@@ -7429,25 +7429,25 @@
         <v>3053.738789062329</v>
       </c>
       <c r="S41" t="n">
-        <v>2769.043670070084</v>
+        <v>3053.738789062329</v>
       </c>
       <c r="T41" t="n">
-        <v>2673.611271652452</v>
+        <v>2676.288706508224</v>
       </c>
       <c r="U41" t="n">
-        <v>2232.983699381128</v>
+        <v>2235.6611342369</v>
       </c>
       <c r="V41" t="n">
-        <v>2232.983699381128</v>
+        <v>1814.599493664351</v>
       </c>
       <c r="W41" t="n">
-        <v>2232.983699381128</v>
+        <v>1384.929315905818</v>
       </c>
       <c r="X41" t="n">
-        <v>1849.870736289544</v>
+        <v>1001.816352814234</v>
       </c>
       <c r="Y41" t="n">
-        <v>1548.539996205901</v>
+        <v>917.6600908828107</v>
       </c>
     </row>
     <row r="42">
@@ -7481,13 +7481,13 @@
         <v>61.84</v>
       </c>
       <c r="J42" t="n">
-        <v>396.666520175299</v>
+        <v>342.8083563952046</v>
       </c>
       <c r="K42" t="n">
-        <v>796.7293362696823</v>
+        <v>742.8711724895879</v>
       </c>
       <c r="L42" t="n">
-        <v>1225.091634084787</v>
+        <v>1225.091634084788</v>
       </c>
       <c r="M42" t="n">
         <v>1522.042175827647</v>
@@ -7496,28 +7496,28 @@
         <v>1866.192460435215</v>
       </c>
       <c r="O42" t="n">
-        <v>2316.104912118933</v>
+        <v>2316.104912118934</v>
       </c>
       <c r="P42" t="n">
-        <v>2639.50425658844</v>
+        <v>2639.504256588441</v>
       </c>
       <c r="Q42" t="n">
-        <v>2679.025784148865</v>
+        <v>2679.025784148866</v>
       </c>
       <c r="R42" t="n">
-        <v>2480.230476522543</v>
+        <v>2341.375483853533</v>
       </c>
       <c r="S42" t="n">
-        <v>2224.105224033037</v>
+        <v>2085.250231364027</v>
       </c>
       <c r="T42" t="n">
-        <v>2029.804451086053</v>
+        <v>1890.949458417043</v>
       </c>
       <c r="U42" t="n">
-        <v>1840.703077590915</v>
+        <v>1701.848084921905</v>
       </c>
       <c r="V42" t="n">
-        <v>1637.156949114632</v>
+        <v>1498.301956445622</v>
       </c>
       <c r="W42" t="n">
         <v>1415.567915872381</v>
@@ -7560,37 +7560,37 @@
         <v>61.84</v>
       </c>
       <c r="J43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="K43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="L43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="M43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="N43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="O43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="P43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="Q43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="R43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="S43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="T43" t="n">
-        <v>61.84</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="U43" t="n">
         <v>91.27831913164476</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1215.452435354799</v>
+        <v>205.6894836373359</v>
       </c>
       <c r="C44" t="n">
-        <v>950.3265987457148</v>
+        <v>61.84</v>
       </c>
       <c r="D44" t="n">
-        <v>724.7314919377858</v>
+        <v>61.84</v>
       </c>
       <c r="E44" t="n">
-        <v>505.1726135470094</v>
+        <v>61.84</v>
       </c>
       <c r="F44" t="n">
-        <v>285.0820794985125</v>
+        <v>61.84</v>
       </c>
       <c r="G44" t="n">
-        <v>285.0820794985125</v>
+        <v>61.84</v>
       </c>
       <c r="H44" t="n">
         <v>61.84</v>
@@ -7639,22 +7639,22 @@
         <v>61.84</v>
       </c>
       <c r="J44" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K44" t="n">
-        <v>61.84</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L44" t="n">
-        <v>612.012076218242</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="M44" t="n">
-        <v>1122.860904947177</v>
+        <v>1673.704308114459</v>
       </c>
       <c r="N44" t="n">
-        <v>1122.860904947177</v>
+        <v>2286.924627889222</v>
       </c>
       <c r="O44" t="n">
-        <v>1888.130904947255</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P44" t="n">
         <v>2653.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3092</v>
       </c>
       <c r="R44" t="n">
-        <v>3092</v>
+        <v>3027.476162799703</v>
       </c>
       <c r="S44" t="n">
-        <v>3092</v>
+        <v>2716.518417544831</v>
       </c>
       <c r="T44" t="n">
-        <v>3092</v>
+        <v>2312.8057087281</v>
       </c>
       <c r="U44" t="n">
-        <v>2744.281976552933</v>
+        <v>1845.91551019415</v>
       </c>
       <c r="V44" t="n">
-        <v>2296.957709717758</v>
+        <v>1398.591243358974</v>
       </c>
       <c r="W44" t="n">
-        <v>1841.024905696598</v>
+        <v>942.6584393378148</v>
       </c>
       <c r="X44" t="n">
-        <v>1841.024905696598</v>
+        <v>533.2828499836049</v>
       </c>
       <c r="Y44" t="n">
-        <v>1513.431539350329</v>
+        <v>205.6894836373359</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1028.890452379605</v>
+        <v>742.1150755498586</v>
       </c>
       <c r="C45" t="n">
-        <v>853.031954959888</v>
+        <v>566.2565781301421</v>
       </c>
       <c r="D45" t="n">
-        <v>690.4686348611986</v>
+        <v>403.6932580314526</v>
       </c>
       <c r="E45" t="n">
-        <v>533.2240922128019</v>
+        <v>246.448715383056</v>
       </c>
       <c r="F45" t="n">
-        <v>379.04606964929</v>
+        <v>92.27069281954398</v>
       </c>
       <c r="G45" t="n">
-        <v>238.9051243209795</v>
+        <v>92.27069281954398</v>
       </c>
       <c r="H45" t="n">
         <v>92.27069281954398</v>
@@ -7727,43 +7727,43 @@
         <v>1201.729797864882</v>
       </c>
       <c r="M45" t="n">
-        <v>1472.940339607742</v>
+        <v>1353.025496521501</v>
       </c>
       <c r="N45" t="n">
-        <v>1791.35062421531</v>
+        <v>1671.435781129069</v>
       </c>
       <c r="O45" t="n">
-        <v>2049.213758290016</v>
+        <v>2095.608232812788</v>
       </c>
       <c r="P45" t="n">
-        <v>2346.873102759523</v>
+        <v>2393.267577282295</v>
       </c>
       <c r="Q45" t="n">
-        <v>2360.654630319948</v>
+        <v>2407.04910484272</v>
       </c>
       <c r="R45" t="n">
-        <v>2343.930332204927</v>
+        <v>2057.154955375181</v>
       </c>
       <c r="S45" t="n">
-        <v>2343.930332204927</v>
+        <v>2057.154955375181</v>
       </c>
       <c r="T45" t="n">
-        <v>2123.366932995317</v>
+        <v>1836.591556165571</v>
       </c>
       <c r="U45" t="n">
-        <v>1908.002933237553</v>
+        <v>1621.227556407807</v>
       </c>
       <c r="V45" t="n">
-        <v>1678.194178498644</v>
+        <v>1391.418801668897</v>
       </c>
       <c r="W45" t="n">
-        <v>1678.194178498644</v>
+        <v>1391.418801668897</v>
       </c>
       <c r="X45" t="n">
-        <v>1442.979290169969</v>
+        <v>1156.203913340223</v>
       </c>
       <c r="Y45" t="n">
-        <v>1228.442529800137</v>
+        <v>941.6671529703906</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="C46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="D46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="E46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="F46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="G46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="H46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="I46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="J46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="K46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="L46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="M46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="N46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="O46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="P46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="R46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="S46" t="n">
+        <v>85.09713788510881</v>
+      </c>
+      <c r="T46" t="n">
         <v>61.84</v>
       </c>
-      <c r="I46" t="n">
-        <v>72.10287893608292</v>
-      </c>
-      <c r="J46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="K46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="L46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="M46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="N46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="O46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="P46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="R46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="S46" t="n">
-        <v>143.672759546362</v>
-      </c>
-      <c r="T46" t="n">
-        <v>120.4156216612533</v>
-      </c>
       <c r="U46" t="n">
-        <v>156.0968142995399</v>
+        <v>97.39038052775143</v>
       </c>
       <c r="V46" t="n">
-        <v>143.8035716568973</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="W46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="X46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
       <c r="Y46" t="n">
-        <v>104.0330566683016</v>
+        <v>85.09713788510881</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>51.24160624509022</v>
       </c>
       <c r="K2" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
-        <v>880.6338033555653</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>70.24786957409242</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814674</v>
+        <v>395.5658246095669</v>
       </c>
       <c r="Q2" t="n">
-        <v>615.8520732695737</v>
+        <v>189.0212843274853</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8207,22 +8207,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>880.6338033555662</v>
       </c>
       <c r="O5" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P5" t="n">
-        <v>532.5116121765154</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q5" t="n">
-        <v>189.0212843274853</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,22 +8441,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>716.8751175230994</v>
+        <v>500.8454983898771</v>
       </c>
       <c r="L8" t="n">
-        <v>403.3848452857261</v>
+        <v>814</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409697</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P8" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8687,16 +8687,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1096.663422488788</v>
+        <v>815.1849144666769</v>
       </c>
       <c r="O11" t="n">
-        <v>231.79875049407</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,22 +8915,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>304.7782794599968</v>
+        <v>505.6444790750808</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9161,16 +9161,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>408.1838259709342</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>334.3735652474629</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,10 +9389,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,13 +9401,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q20" t="n">
-        <v>334.3735652474629</v>
+        <v>237.2486827705622</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,19 +9626,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>584.2070019471741</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>505.6444790750808</v>
       </c>
       <c r="P23" t="n">
         <v>814.2870600406815</v>
@@ -9863,13 +9863,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>314.0531751575267</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>657.4491031847872</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
         <v>1096.663422488788</v>
@@ -9878,7 +9878,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.287060040709</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10103,13 +10103,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>544.2621276423173</v>
+        <v>601.3242207078167</v>
       </c>
       <c r="N29" t="n">
-        <v>823.7549044963758</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
         <v>843.2478695741272</v>
@@ -10118,7 +10118,7 @@
         <v>773.2870600407163</v>
       </c>
       <c r="Q29" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10340,7 +10340,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>375.2922462381605</v>
+        <v>29.9389351802052</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
@@ -10352,10 +10352,10 @@
         <v>843.2478695741345</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407235</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>188.2053843274865</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>80.27785409340403</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1012.590174281182</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>1096.663422488788</v>
+        <v>498.0894691118057</v>
       </c>
       <c r="O35" t="n">
         <v>843.2478695741418</v>
@@ -10814,22 +10814,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>772.9999999999998</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>944.9816690253347</v>
       </c>
       <c r="N38" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>520.8080175723416</v>
+        <v>843.247869574149</v>
       </c>
       <c r="P38" t="n">
-        <v>15.66976004068272</v>
+        <v>773.2870600407381</v>
       </c>
       <c r="Q38" t="n">
-        <v>188.2053843274866</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>603.4970285184673</v>
       </c>
       <c r="L41" t="n">
-        <v>709.3149054985569</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
         <v>843.2478695741563</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407454</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>555.7293699174162</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>843.2478695741709</v>
+        <v>440.4259272085471</v>
       </c>
       <c r="P44" t="n">
-        <v>773.2870600407599</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22703,7 +22703,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>5.662449696452001</v>
+        <v>5.662449696444355</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>29.21007785422734</v>
+        <v>29.21007785422415</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.662449696454928</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>29.21007785422643</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23226,16 +23226,16 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>61.28925813745596</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>10.72844246949276</v>
       </c>
       <c r="G11" t="n">
         <v>178.7573722870162</v>
@@ -23423,13 +23423,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23469,16 +23469,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>86.30994672070055</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>157.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>235.4209499110585</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23657,16 +23657,16 @@
         <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>389.445564079015</v>
+        <v>297.3129142515843</v>
       </c>
       <c r="P16" t="n">
-        <v>436.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>421.860847251041</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23709,10 +23709,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.4306086145859922</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4306086145860206</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23946,7 +23946,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4306086145859922</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24092,7 +24092,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -24122,10 +24122,10 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>16.50004144370942</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N22" t="n">
         <v>292.1850752716849</v>
@@ -24134,13 +24134,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4306086145172685</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24368,16 +24368,16 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>430.4918320509147</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24408,10 +24408,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -24456,19 +24456,19 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>357.2076936691876</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>254.7062278091485</v>
       </c>
     </row>
     <row r="27">
@@ -24602,13 +24602,13 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>346.1850752716849</v>
+        <v>5.408275783157251</v>
       </c>
       <c r="O28" t="n">
         <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
         <v>500.839266425598</v>
@@ -24660,10 +24660,10 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>64.34288438841924</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24699,13 +24699,13 @@
         <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>309.8982579119931</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -24851,7 +24851,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>160.8253284926234</v>
+        <v>159.4525186539137</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -24866,7 +24866,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
         <v>22.44364543010755</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>51.31795371660975</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -25079,7 +25079,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>51.31795371660968</v>
       </c>
       <c r="P34" t="n">
         <v>396.4478973282775</v>
@@ -25310,19 +25310,19 @@
         <v>132.5476281577792</v>
       </c>
       <c r="M37" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>240.2408026384947</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>35.03314761542316</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
         <v>435.6021279811511</v>
@@ -25556,16 +25556,16 @@
         <v>349.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>396.4478973282775</v>
+        <v>326.3973665406309</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.322948915208713</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25596,10 +25596,10 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>197.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -25608,7 +25608,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -25644,25 +25644,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>281.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>279.197507295108</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>416.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>425.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>215.0027333706972</v>
       </c>
     </row>
     <row r="42">
@@ -25720,7 +25720,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>137.4664427423205</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>137.4664427423195</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25830,25 +25830,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>294.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>120.0635894420314</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>217.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>217.8896287080119</v>
       </c>
       <c r="G44" t="n">
         <v>216.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>221.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25878,16 +25878,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>63.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>307.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>399.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>117.9804533360143</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -25896,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>405.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -25924,10 +25924,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>138.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>145.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25957,7 +25957,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>343.7167421585088</v>
+        <v>13.87858931951558</v>
       </c>
       <c r="S45" t="n">
         <v>279.5639999646113</v>
@@ -26006,7 +26006,7 @@
         <v>58.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41.77112610161862</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26051,7 +26051,7 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>39.37280983870968</v>
       </c>
       <c r="X46" t="n">
         <v>60.44364543010755</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>933102.2884272019</v>
+        <v>933102.2884272021</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1688307.887505657</v>
+        <v>1688307.887505658</v>
       </c>
     </row>
     <row r="4">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3117307.494280312</v>
+        <v>3117307.494280313</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3820477.704130512</v>
+        <v>3820477.704130513</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4551971.299678596</v>
+        <v>4551971.299678598</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5283464.895226677</v>
+        <v>5283464.895226679</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6014958.490774762</v>
+        <v>6014958.490774761</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6678453.789106591</v>
+        <v>6678453.78910659</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7346471.975519229</v>
+        <v>7346471.975519228</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8083794.357796866</v>
+        <v>8083794.357796864</v>
       </c>
     </row>
     <row r="13">
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1447477.398233708</v>
+        <v>1447477.398233707</v>
       </c>
       <c r="C2" t="n">
         <v>1447477.398233707</v>
@@ -26278,7 +26278,7 @@
         <v>1447477.398233707</v>
       </c>
       <c r="E2" t="n">
-        <v>1294933.376336229</v>
+        <v>1294933.37633623</v>
       </c>
       <c r="F2" t="n">
         <v>1347742.902212884</v>
@@ -26287,10 +26287,10 @@
         <v>1402029.391467165</v>
       </c>
       <c r="H2" t="n">
+        <v>1402029.391467166</v>
+      </c>
+      <c r="I2" t="n">
         <v>1402029.391467165</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1402029.391467172</v>
       </c>
       <c r="J2" t="n">
         <v>1280368.19062423</v>
@@ -26302,10 +26302,10 @@
         <v>1409931.16836822</v>
       </c>
       <c r="M2" t="n">
-        <v>1409931.168368219</v>
+        <v>1409931.16836822</v>
       </c>
       <c r="N2" t="n">
-        <v>1409931.168368219</v>
+        <v>1409931.16836822</v>
       </c>
       <c r="O2" t="n">
         <v>1242152.287210232</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>614247.5715792079</v>
+        <v>619095.9472656923</v>
       </c>
       <c r="C4" t="n">
-        <v>612495.6628399484</v>
+        <v>617344.0385264327</v>
       </c>
       <c r="D4" t="n">
-        <v>610741.3775271378</v>
+        <v>615589.7532136219</v>
       </c>
       <c r="E4" t="n">
-        <v>532123.6038252711</v>
+        <v>536922.2846154375</v>
       </c>
       <c r="F4" t="n">
-        <v>556398.2196192667</v>
+        <v>561196.9004094332</v>
       </c>
       <c r="G4" t="n">
-        <v>581187.6277435899</v>
+        <v>585986.3085337563</v>
       </c>
       <c r="H4" t="n">
-        <v>579514.6928034928</v>
+        <v>584313.3735936591</v>
       </c>
       <c r="I4" t="n">
-        <v>577839.4224190691</v>
+        <v>582638.1032092323</v>
       </c>
       <c r="J4" t="n">
-        <v>520323.0592843113</v>
+        <v>524998.4738086244</v>
       </c>
       <c r="K4" t="n">
-        <v>518858.3176303694</v>
+        <v>523533.7321546826</v>
       </c>
       <c r="L4" t="n">
-        <v>581043.8351797324</v>
+        <v>585765.748114326</v>
       </c>
       <c r="M4" t="n">
-        <v>579313.7164781794</v>
+        <v>584035.6294127734</v>
       </c>
       <c r="N4" t="n">
-        <v>577581.1101536271</v>
+        <v>582303.0230882207</v>
       </c>
       <c r="O4" t="n">
-        <v>494869.5309141541</v>
+        <v>499544.9454384673</v>
       </c>
       <c r="P4" t="n">
-        <v>454063.7935190182</v>
+        <v>458739.2080433314</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>463583.0266544996</v>
+        <v>458734.6509680146</v>
       </c>
       <c r="C6" t="n">
-        <v>751862.9353937586</v>
+        <v>747014.5597072747</v>
       </c>
       <c r="D6" t="n">
-        <v>753617.2207065695</v>
+        <v>748768.8450200849</v>
       </c>
       <c r="E6" t="n">
-        <v>514403.0475109584</v>
+        <v>509604.3667207925</v>
       </c>
       <c r="F6" t="n">
-        <v>699952.1635936172</v>
+        <v>695153.4828034507</v>
       </c>
       <c r="G6" t="n">
-        <v>725495.3127235753</v>
+        <v>720696.6319334087</v>
       </c>
       <c r="H6" t="n">
-        <v>749568.247663672</v>
+        <v>744769.5668735065</v>
       </c>
       <c r="I6" t="n">
-        <v>751243.5180481026</v>
+        <v>746444.8372579331</v>
       </c>
       <c r="J6" t="n">
-        <v>285235.2063399184</v>
+        <v>280559.7918156057</v>
       </c>
       <c r="K6" t="n">
-        <v>674795.9479938606</v>
+        <v>670120.5334695478</v>
       </c>
       <c r="L6" t="n">
-        <v>682224.8541884876</v>
+        <v>677502.941253894</v>
       </c>
       <c r="M6" t="n">
-        <v>759154.9728900399</v>
+        <v>754433.059955447</v>
       </c>
       <c r="N6" t="n">
-        <v>760887.579214592</v>
+        <v>756165.6662799988</v>
       </c>
       <c r="O6" t="n">
-        <v>607977.6592960778</v>
+        <v>603302.2447717648</v>
       </c>
       <c r="P6" t="n">
-        <v>641816.6910051211</v>
+        <v>637141.2764808077</v>
       </c>
     </row>
   </sheetData>
@@ -26990,7 +26990,7 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -27005,10 +27005,10 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27442,7 +27442,7 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>400</v>
@@ -27454,7 +27454,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>157.3092074428804</v>
+        <v>56.51176829727007</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27493,7 +27493,7 @@
         <v>400</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W2" t="n">
         <v>400</v>
@@ -27518,7 +27518,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>33.07798428065587</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27527,13 +27527,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,10 +27560,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27572,7 +27572,7 @@
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>342.2743756165777</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27597,28 +27597,28 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>384.1335474495087</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>35.26894883590776</v>
+        <v>311.0452421485497</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,16 +27642,16 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27688,7 +27688,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27718,13 +27718,13 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>307.3903671255644</v>
+        <v>56.5117682972699</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27739,7 +27739,7 @@
         <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -27761,10 +27761,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -27806,16 +27806,16 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>207.6501538294815</v>
+        <v>342.2743756165772</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27837,13 +27837,13 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>272.2156529028853</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>345.8674771514767</v>
       </c>
     </row>
     <row r="8">
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>56.51176829727086</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27955,25 +27955,25 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
       </c>
       <c r="V8" t="n">
-        <v>400</v>
+        <v>307.3903671255647</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
       </c>
       <c r="X8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>400</v>
@@ -27992,16 +27992,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>158.6236956112199</v>
+        <v>172.5204020740694</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
         <v>332.1680871864211</v>
@@ -28086,13 +28086,13 @@
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T10" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U10" t="n">
         <v>400</v>
       </c>
-      <c r="T10" t="n">
-        <v>295.8364148149694</v>
-      </c>
-      <c r="U10" t="n">
-        <v>150.9583912744579</v>
-      </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>347.3202976645084</v>
       </c>
       <c r="X10" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28247,7 +28247,7 @@
         <v>225</v>
       </c>
       <c r="J12" t="n">
-        <v>19.11687125883891</v>
+        <v>225</v>
       </c>
       <c r="K12" t="n">
         <v>225</v>
@@ -28265,7 +28265,7 @@
         <v>225</v>
       </c>
       <c r="P12" t="n">
-        <v>225</v>
+        <v>19.11687125883863</v>
       </c>
       <c r="Q12" t="n">
         <v>225</v>
@@ -28487,19 +28487,19 @@
         <v>251</v>
       </c>
       <c r="K15" t="n">
-        <v>166.1982915220773</v>
+        <v>251</v>
       </c>
       <c r="L15" t="n">
         <v>251</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>166.1982915220776</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -28718,16 +28718,16 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>155.6705902671031</v>
       </c>
       <c r="L18" t="n">
-        <v>217.5442043757544</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -28736,7 +28736,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -28961,7 +28961,7 @@
         <v>279</v>
       </c>
       <c r="K21" t="n">
-        <v>261.5913251766236</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -28976,10 +28976,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>155.6705902671034</v>
       </c>
       <c r="Q21" t="n">
-        <v>173.0792650904796</v>
+        <v>279</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988283643</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29195,10 +29195,10 @@
         <v>279</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="K24" t="n">
-        <v>279</v>
+        <v>261.5913251766236</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -29210,13 +29210,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>155.6705902671033</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29438,13 +29438,13 @@
         <v>225</v>
       </c>
       <c r="L27" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="M27" t="n">
         <v>225</v>
       </c>
       <c r="N27" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="O27" t="n">
         <v>225</v>
@@ -29666,7 +29666,7 @@
         <v>225</v>
       </c>
       <c r="I30" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J30" t="n">
         <v>225</v>
@@ -29684,10 +29684,10 @@
         <v>225</v>
       </c>
       <c r="O30" t="n">
+        <v>19.11687125883898</v>
+      </c>
+      <c r="P30" t="n">
         <v>225</v>
-      </c>
-      <c r="P30" t="n">
-        <v>26.99048536749045</v>
       </c>
       <c r="Q30" t="n">
         <v>225</v>
@@ -29803,7 +29803,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="C32" t="n">
         <v>291</v>
@@ -29824,7 +29824,7 @@
         <v>291</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>141.6245682972704</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29903,11 +29903,11 @@
         <v>291</v>
       </c>
       <c r="I33" t="n">
+        <v>291</v>
+      </c>
+      <c r="J33" t="n">
         <v>227.015861157829</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
@@ -29918,7 +29918,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -30143,28 +30143,28 @@
         <v>291</v>
       </c>
       <c r="J36" t="n">
+        <v>227.015861157829</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>291</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>227.0158611578291</v>
       </c>
       <c r="R36" t="n">
         <v>291</v>
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
       <c r="C37" t="n">
         <v>291</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S38" t="n">
         <v>291</v>
@@ -30334,7 +30334,7 @@
         <v>291</v>
       </c>
       <c r="U38" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="V38" t="n">
         <v>291</v>
@@ -30377,19 +30377,19 @@
         <v>291</v>
       </c>
       <c r="I39" t="n">
+        <v>227.0158611578289</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>291</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>227.0158611578289</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -30617,13 +30617,13 @@
         <v>213</v>
       </c>
       <c r="J42" t="n">
-        <v>213</v>
+        <v>158.597814363541</v>
       </c>
       <c r="K42" t="n">
         <v>213</v>
       </c>
       <c r="L42" t="n">
-        <v>158.5978143635403</v>
+        <v>213</v>
       </c>
       <c r="M42" t="n">
         <v>213</v>
@@ -30696,7 +30696,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>35.26894883590776</v>
+        <v>65.00462472645802</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30729,7 +30729,7 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U43" t="n">
-        <v>180.6940671650082</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V43" t="n">
         <v>199.1703102162162</v>
@@ -30863,13 +30863,13 @@
         <v>187</v>
       </c>
       <c r="M45" t="n">
-        <v>187</v>
+        <v>65.87389587248394</v>
       </c>
       <c r="N45" t="n">
         <v>187</v>
       </c>
       <c r="O45" t="n">
-        <v>19.01079029392637</v>
+        <v>187</v>
       </c>
       <c r="P45" t="n">
         <v>187</v>
@@ -30930,10 +30930,10 @@
         <v>187</v>
       </c>
       <c r="I46" t="n">
-        <v>187</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>107.5617575331594</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -30966,7 +30966,7 @@
         <v>187</v>
       </c>
       <c r="U46" t="n">
-        <v>187</v>
+        <v>186.8678665550149</v>
       </c>
       <c r="V46" t="n">
         <v>187</v>
@@ -34749,7 +34749,7 @@
         <v>814.0000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>814</v>
@@ -34883,28 +34883,28 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>139.0896746079787</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>275.776293312642</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,16 +34928,16 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -35123,13 +35123,13 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>121.2572616284273</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>58.40212430201439</v>
       </c>
     </row>
     <row r="8">
@@ -35220,7 +35220,7 @@
         <v>814</v>
       </c>
       <c r="K8" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -35232,7 +35232,7 @@
         <v>814</v>
       </c>
       <c r="O8" t="n">
-        <v>814.0000000000045</v>
+        <v>814</v>
       </c>
       <c r="P8" t="n">
         <v>814</v>
@@ -35372,13 +35372,13 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>85.81184830871172</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>120.9474878257987</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35466,16 +35466,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>619.4144644189528</v>
+        <v>337.9359563968417</v>
       </c>
       <c r="O11" t="n">
-        <v>161.5508809199775</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35533,7 +35533,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
-        <v>144.3254774965146</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
         <v>416.1038546407913</v>
@@ -35551,7 +35551,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734918</v>
       </c>
       <c r="Q12" t="n">
         <v>51.92073490952041</v>
@@ -35694,22 +35694,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>234.5304098859044</v>
+        <v>435.3966095009883</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35773,19 +35773,19 @@
         <v>376.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>357.3021461628686</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L15" t="n">
         <v>525.0913753486871</v>
       </c>
       <c r="M15" t="n">
-        <v>86.95004216450428</v>
+        <v>253.1483336865819</v>
       </c>
       <c r="N15" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>492.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
         <v>113.6660045146532</v>
@@ -35940,16 +35940,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>337.9359563968417</v>
+        <v>814</v>
       </c>
       <c r="P17" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>161.5508809199775</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36004,16 +36004,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>125.2086062376757</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>191.1038546407913</v>
+        <v>346.7744449078945</v>
       </c>
       <c r="L18" t="n">
-        <v>491.6355797244414</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
         <v>86.95004216450428</v>
@@ -36022,7 +36022,7 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P18" t="n">
         <v>113.6660045146532</v>
@@ -36168,10 +36168,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,13 +36180,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q20" t="n">
-        <v>161.5508809199775</v>
+        <v>64.42599844307681</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36247,7 +36247,7 @@
         <v>404.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>452.6951798174148</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>274.091375348687</v>
@@ -36262,10 +36262,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>113.6660045146532</v>
+        <v>269.3365947817566</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36405,19 +36405,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>39.94487430485688</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>435.3966095009883</v>
       </c>
       <c r="P23" t="n">
         <v>814</v>
@@ -36426,7 +36426,7 @@
         <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
-        <v>6.981979528761874e-11</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36481,10 +36481,10 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
-        <v>125.2086062376757</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>470.1038546407913</v>
+        <v>452.6951798174148</v>
       </c>
       <c r="L24" t="n">
         <v>274.091375348687</v>
@@ -36496,13 +36496,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>397.1276121698497</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36642,13 +36642,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>314.0531751575267</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>113.18697554247</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
         <v>619.4144644189528</v>
@@ -36657,7 +36657,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>773.0000000000275</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36724,13 +36724,13 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075261</v>
       </c>
       <c r="M27" t="n">
         <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>153.743421367494</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O27" t="n">
         <v>466.4570219027464</v>
@@ -36882,13 +36882,13 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>772.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>57.06209306549945</v>
       </c>
       <c r="N29" t="n">
-        <v>346.5059464265406</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
         <v>773.0000000000348</v>
@@ -36897,7 +36897,7 @@
         <v>773.0000000000348</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
         <v>350.2086062376757</v>
@@ -36970,10 +36970,10 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O30" t="n">
-        <v>466.4570219027464</v>
+        <v>260.5738931615854</v>
       </c>
       <c r="P30" t="n">
-        <v>140.6564898821437</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q30" t="n">
         <v>51.92073490952041</v>
@@ -37116,10 +37116,10 @@
         <v>773.0000000000421</v>
       </c>
       <c r="K32" t="n">
+        <v>727.1079320763233</v>
+      </c>
+      <c r="L32" t="n">
         <v>773</v>
-      </c>
-      <c r="L32" t="n">
-        <v>727.1079320763574</v>
       </c>
       <c r="M32" t="n">
         <v>773.0000000000421</v>
@@ -37189,10 +37189,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>9.889475266480432</v>
+        <v>73.87361410865147</v>
       </c>
       <c r="J33" t="n">
-        <v>125.2086062376757</v>
+        <v>352.2244673955047</v>
       </c>
       <c r="K33" t="n">
         <v>191.1038546407913</v>
@@ -37204,7 +37204,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>425.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
         <v>241.4570219027464</v>
@@ -37353,10 +37353,10 @@
         <v>773.0000000000493</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320760064</v>
+        <v>773</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>727.1079320762534</v>
       </c>
       <c r="M35" t="n">
         <v>773.0000000000493</v>
@@ -37429,7 +37429,7 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J36" t="n">
-        <v>416.2086062376757</v>
+        <v>352.2244673955047</v>
       </c>
       <c r="K36" t="n">
         <v>191.1038546407913</v>
@@ -37450,7 +37450,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>53.93659606734953</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37484,7 +37484,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.886199662921342</v>
+        <v>3.886199662945266</v>
       </c>
       <c r="C37" t="n">
         <v>18.27475335195533</v>
@@ -37590,7 +37590,7 @@
         <v>773.0000000000566</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320760109</v>
+        <v>727.1079320759773</v>
       </c>
       <c r="L38" t="n">
         <v>773</v>
@@ -37663,7 +37663,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>73.87361410865147</v>
+        <v>9.889475266480316</v>
       </c>
       <c r="J39" t="n">
         <v>125.2086062376757</v>
@@ -37675,7 +37675,7 @@
         <v>274.091375348687</v>
       </c>
       <c r="M39" t="n">
-        <v>313.9659033223331</v>
+        <v>377.9500421645043</v>
       </c>
       <c r="N39" t="n">
         <v>134.6265501086548</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>603.4970285184673</v>
       </c>
       <c r="L41" t="n">
-        <v>709.3149054985569</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>773.0000000000639</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>773.0000000000639</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,13 +37903,13 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>338.2086062376757</v>
+        <v>283.8064206012167</v>
       </c>
       <c r="K42" t="n">
         <v>404.1038546407913</v>
       </c>
       <c r="L42" t="n">
-        <v>432.6891897122273</v>
+        <v>487.091375348687</v>
       </c>
       <c r="M42" t="n">
         <v>299.9500421645043</v>
@@ -37982,7 +37982,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>29.73567589055027</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>29.73567589055027</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>555.7293699174162</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>773.0000000000784</v>
+        <v>370.1780576344547</v>
       </c>
       <c r="P44" t="n">
-        <v>773.0000000000784</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38149,13 +38149,13 @@
         <v>461.091375348687</v>
       </c>
       <c r="M45" t="n">
-        <v>273.9500421645043</v>
+        <v>152.8239380369882</v>
       </c>
       <c r="N45" t="n">
         <v>321.6265501086548</v>
       </c>
       <c r="O45" t="n">
-        <v>260.4678121966728</v>
+        <v>428.4570219027464</v>
       </c>
       <c r="P45" t="n">
         <v>300.6660045146532</v>
@@ -38216,10 +38216,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>10.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>72.29280869725164</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>36.04160872554206</v>
+        <v>35.909475280557</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
